--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,3197 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121515933</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>593834</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7183112</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121515926</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593785</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7183163</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121515938</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593866</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7183116</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121515924</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593759</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7183183</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121515927</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593785</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7183164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121515929</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593799</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7183161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121515951</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7182928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121515946</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7183052</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121515942</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593940</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7183055</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121515941</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593896</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7183092</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121515928</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>593793</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7183160</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121515943</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>593939</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7183054</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121515948</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>593958</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7183050</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121515940</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>593895</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7183091</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121515931</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>593808</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7183154</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121515939</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>593874</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7183112</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121515932</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>593807</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7183156</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121515936</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>593845</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7183110</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121515953</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594162</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7182917</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121515944</v>
+      </c>
+      <c r="B22" t="n">
+        <v>77544</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>593959</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7183054</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121515937</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>593844</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7183109</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121515949</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594135</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7182928</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121515923</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>593761</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7183183</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121515935</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>593842</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7183114</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121515947</v>
+      </c>
+      <c r="B27" t="n">
+        <v>74713</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>593958</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7183049</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121515954</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>594162</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7182918</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121515934</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>593840</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7183113</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121515930</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>593799</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7183160</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515933</v>
+        <v>121515939</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593834</v>
+        <v>593874</v>
       </c>
       <c r="R3" t="n">
         <v>7183112</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515926</v>
+        <v>121515936</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593785</v>
+        <v>593845</v>
       </c>
       <c r="R4" t="n">
-        <v>7183163</v>
+        <v>7183110</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515938</v>
+        <v>121515932</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1046,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593866</v>
+        <v>593807</v>
       </c>
       <c r="R5" t="n">
-        <v>7183116</v>
+        <v>7183156</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515924</v>
+        <v>121515954</v>
       </c>
       <c r="B6" t="n">
         <v>78607</v>
@@ -1192,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593759</v>
+        <v>594162</v>
       </c>
       <c r="R6" t="n">
-        <v>7183183</v>
+        <v>7182918</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515927</v>
+        <v>121515944</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>77544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593785</v>
+        <v>593959</v>
       </c>
       <c r="R7" t="n">
-        <v>7183164</v>
+        <v>7183054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515929</v>
+        <v>121515931</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1412,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593799</v>
+        <v>593808</v>
       </c>
       <c r="R8" t="n">
-        <v>7183161</v>
+        <v>7183154</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515951</v>
+        <v>121515942</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1499,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594136</v>
+        <v>593940</v>
       </c>
       <c r="R9" t="n">
-        <v>7182928</v>
+        <v>7183055</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515946</v>
+        <v>121515928</v>
       </c>
       <c r="B10" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593959</v>
+        <v>593793</v>
       </c>
       <c r="R10" t="n">
-        <v>7183052</v>
+        <v>7183160</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515942</v>
+        <v>121515941</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,39 +1733,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593940</v>
+        <v>593896</v>
       </c>
       <c r="R11" t="n">
-        <v>7183055</v>
+        <v>7183092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515941</v>
+        <v>121515949</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,21 +1845,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593896</v>
+        <v>594135</v>
       </c>
       <c r="R12" t="n">
-        <v>7183092</v>
+        <v>7182928</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515928</v>
+        <v>121515948</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,39 +1957,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593793</v>
+        <v>593958</v>
       </c>
       <c r="R13" t="n">
-        <v>7183160</v>
+        <v>7183050</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515943</v>
+        <v>121515933</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,34 +2069,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593939</v>
+        <v>593834</v>
       </c>
       <c r="R14" t="n">
-        <v>7183054</v>
+        <v>7183112</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2138,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515948</v>
+        <v>121515924</v>
       </c>
       <c r="B15" t="n">
         <v>78607</v>
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593958</v>
+        <v>593759</v>
       </c>
       <c r="R15" t="n">
-        <v>7183050</v>
+        <v>7183183</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2250,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515940</v>
+        <v>121515929</v>
       </c>
       <c r="B16" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,34 +2298,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593895</v>
+        <v>593799</v>
       </c>
       <c r="R16" t="n">
-        <v>7183091</v>
+        <v>7183161</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515931</v>
+        <v>121515940</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,39 +2415,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593808</v>
+        <v>593895</v>
       </c>
       <c r="R17" t="n">
-        <v>7183154</v>
+        <v>7183091</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515939</v>
+        <v>121515937</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,39 +2527,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593874</v>
+        <v>593844</v>
       </c>
       <c r="R18" t="n">
-        <v>7183112</v>
+        <v>7183109</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2596,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515932</v>
+        <v>121515923</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,34 +2639,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593807</v>
+        <v>593761</v>
       </c>
       <c r="R19" t="n">
-        <v>7183156</v>
+        <v>7183183</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515936</v>
+        <v>121515934</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2756,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2785,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593845</v>
+        <v>593840</v>
       </c>
       <c r="R20" t="n">
-        <v>7183110</v>
+        <v>7183113</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2857,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515953</v>
+        <v>121515947</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>74713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,39 +2868,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594162</v>
+        <v>593958</v>
       </c>
       <c r="R21" t="n">
-        <v>7182917</v>
+        <v>7183049</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515944</v>
+        <v>121515946</v>
       </c>
       <c r="B22" t="n">
-        <v>77544</v>
+        <v>82391</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,21 +2980,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3017,7 +3007,7 @@
         <v>593959</v>
       </c>
       <c r="R22" t="n">
-        <v>7183054</v>
+        <v>7183052</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3086,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515937</v>
+        <v>121515925</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,34 +3092,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593844</v>
+        <v>593785</v>
       </c>
       <c r="R23" t="n">
-        <v>7183109</v>
+        <v>7183163</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515949</v>
+        <v>121515927</v>
       </c>
       <c r="B24" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,21 +3209,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594135</v>
+        <v>593785</v>
       </c>
       <c r="R24" t="n">
-        <v>7182928</v>
+        <v>7183164</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,7 +3305,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515923</v>
+        <v>121515953</v>
       </c>
       <c r="B25" t="n">
         <v>57354</v>
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593761</v>
+        <v>594162</v>
       </c>
       <c r="R25" t="n">
-        <v>7183183</v>
+        <v>7182917</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3390,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,7 +3422,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515935</v>
+        <v>121515938</v>
       </c>
       <c r="B26" t="n">
         <v>57354</v>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593842</v>
+        <v>593866</v>
       </c>
       <c r="R26" t="n">
-        <v>7183114</v>
+        <v>7183116</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3507,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515947</v>
+        <v>121515935</v>
       </c>
       <c r="B27" t="n">
-        <v>74713</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,34 +3555,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593958</v>
+        <v>593842</v>
       </c>
       <c r="R27" t="n">
-        <v>7183049</v>
+        <v>7183114</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,7 +3656,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515954</v>
+        <v>121515951</v>
       </c>
       <c r="B28" t="n">
         <v>78607</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594162</v>
+        <v>594136</v>
       </c>
       <c r="R28" t="n">
-        <v>7182918</v>
+        <v>7182928</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515934</v>
+        <v>121515930</v>
       </c>
       <c r="B29" t="n">
         <v>78607</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593840</v>
+        <v>593799</v>
       </c>
       <c r="R29" t="n">
-        <v>7183113</v>
+        <v>7183160</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515930</v>
+        <v>121515943</v>
       </c>
       <c r="B30" t="n">
         <v>78607</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593799</v>
+        <v>593939</v>
       </c>
       <c r="R30" t="n">
-        <v>7183160</v>
+        <v>7183054</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -1941,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515948</v>
+        <v>121515933</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1957,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593958</v>
+        <v>593834</v>
       </c>
       <c r="R13" t="n">
-        <v>7183050</v>
+        <v>7183112</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515933</v>
+        <v>121515924</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,39 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593834</v>
+        <v>593759</v>
       </c>
       <c r="R14" t="n">
-        <v>7183112</v>
+        <v>7183183</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515924</v>
+        <v>121515948</v>
       </c>
       <c r="B15" t="n">
         <v>78607</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593759</v>
+        <v>593958</v>
       </c>
       <c r="R15" t="n">
-        <v>7183183</v>
+        <v>7183050</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515939</v>
+        <v>121515943</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593874</v>
+        <v>593939</v>
       </c>
       <c r="R3" t="n">
-        <v>7183112</v>
+        <v>7183054</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515936</v>
+        <v>121515925</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +929,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593845</v>
+        <v>593785</v>
       </c>
       <c r="R4" t="n">
-        <v>7183110</v>
+        <v>7183163</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515932</v>
+        <v>121515947</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593807</v>
+        <v>593958</v>
       </c>
       <c r="R5" t="n">
-        <v>7183156</v>
+        <v>7183049</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515954</v>
+        <v>121515936</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594162</v>
+        <v>593845</v>
       </c>
       <c r="R6" t="n">
-        <v>7182918</v>
+        <v>7183110</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515944</v>
+        <v>121515954</v>
       </c>
       <c r="B7" t="n">
-        <v>77544</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R7" t="n">
-        <v>7183054</v>
+        <v>7182918</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515931</v>
+        <v>121515938</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593808</v>
+        <v>593866</v>
       </c>
       <c r="R8" t="n">
-        <v>7183154</v>
+        <v>7183116</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515942</v>
+        <v>121515953</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593940</v>
+        <v>594162</v>
       </c>
       <c r="R9" t="n">
-        <v>7183055</v>
+        <v>7182917</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515928</v>
+        <v>121515924</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1616,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593793</v>
+        <v>593759</v>
       </c>
       <c r="R10" t="n">
-        <v>7183160</v>
+        <v>7183183</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515941</v>
+        <v>121515928</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,34 +1728,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593896</v>
+        <v>593793</v>
       </c>
       <c r="R11" t="n">
-        <v>7183092</v>
+        <v>7183160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515949</v>
+        <v>121515929</v>
       </c>
       <c r="B12" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,34 +1845,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594135</v>
+        <v>593799</v>
       </c>
       <c r="R12" t="n">
-        <v>7182928</v>
+        <v>7183161</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515933</v>
+        <v>121515923</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,7 +1982,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593834</v>
+        <v>593761</v>
       </c>
       <c r="R13" t="n">
-        <v>7183112</v>
+        <v>7183183</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515924</v>
+        <v>121515942</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,34 +2079,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593759</v>
+        <v>593940</v>
       </c>
       <c r="R14" t="n">
-        <v>7183183</v>
+        <v>7183055</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515948</v>
+        <v>121515930</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,10 +2220,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593958</v>
+        <v>593799</v>
       </c>
       <c r="R15" t="n">
-        <v>7183050</v>
+        <v>7183160</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515929</v>
+        <v>121515932</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,39 +2308,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593799</v>
+        <v>593807</v>
       </c>
       <c r="R16" t="n">
-        <v>7183161</v>
+        <v>7183156</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515940</v>
+        <v>121515944</v>
       </c>
       <c r="B17" t="n">
-        <v>82391</v>
+        <v>77545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,21 +2420,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593895</v>
+        <v>593959</v>
       </c>
       <c r="R17" t="n">
-        <v>7183091</v>
+        <v>7183054</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,7 +2519,7 @@
         <v>121515937</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2623,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515923</v>
+        <v>121515933</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,7 +2664,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593761</v>
+        <v>593834</v>
       </c>
       <c r="R19" t="n">
-        <v>7183183</v>
+        <v>7183112</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515934</v>
+        <v>121515949</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2780,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593840</v>
+        <v>594135</v>
       </c>
       <c r="R20" t="n">
-        <v>7183113</v>
+        <v>7182928</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515947</v>
+        <v>121515935</v>
       </c>
       <c r="B21" t="n">
-        <v>74713</v>
+        <v>57355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,34 +2873,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593958</v>
+        <v>593842</v>
       </c>
       <c r="R21" t="n">
-        <v>7183049</v>
+        <v>7183114</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2927,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515946</v>
+        <v>121515948</v>
       </c>
       <c r="B22" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,21 +2990,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593959</v>
+        <v>593958</v>
       </c>
       <c r="R22" t="n">
-        <v>7183052</v>
+        <v>7183050</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3076,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515925</v>
+        <v>121515939</v>
       </c>
       <c r="B23" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,7 +3122,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593785</v>
+        <v>593874</v>
       </c>
       <c r="R23" t="n">
-        <v>7183163</v>
+        <v>7183112</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515927</v>
+        <v>121515931</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,34 +3219,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593785</v>
+        <v>593808</v>
       </c>
       <c r="R24" t="n">
-        <v>7183164</v>
+        <v>7183154</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3268,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515953</v>
+        <v>121515941</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,39 +3336,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594162</v>
+        <v>593896</v>
       </c>
       <c r="R25" t="n">
-        <v>7182917</v>
+        <v>7183092</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515938</v>
+        <v>121515940</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,39 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593866</v>
+        <v>593895</v>
       </c>
       <c r="R26" t="n">
-        <v>7183116</v>
+        <v>7183091</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3502,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515935</v>
+        <v>121515934</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3555,39 +3560,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593842</v>
+        <v>593840</v>
       </c>
       <c r="R27" t="n">
-        <v>7183114</v>
+        <v>7183113</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515951</v>
+        <v>121515927</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594136</v>
+        <v>593785</v>
       </c>
       <c r="R28" t="n">
-        <v>7182928</v>
+        <v>7183164</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515930</v>
+        <v>121515946</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593799</v>
+        <v>593959</v>
       </c>
       <c r="R29" t="n">
-        <v>7183160</v>
+        <v>7183052</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515943</v>
+        <v>121515951</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593939</v>
+        <v>594136</v>
       </c>
       <c r="R30" t="n">
-        <v>7183054</v>
+        <v>7182928</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515943</v>
+        <v>121515940</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593939</v>
+        <v>593895</v>
       </c>
       <c r="R3" t="n">
-        <v>7183054</v>
+        <v>7183091</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515925</v>
+        <v>121515929</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593785</v>
+        <v>593799</v>
       </c>
       <c r="R4" t="n">
-        <v>7183163</v>
+        <v>7183161</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515947</v>
+        <v>121515948</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>593958</v>
       </c>
       <c r="R5" t="n">
-        <v>7183049</v>
+        <v>7183050</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515936</v>
+        <v>121515927</v>
       </c>
       <c r="B6" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593845</v>
+        <v>593785</v>
       </c>
       <c r="R6" t="n">
-        <v>7183110</v>
+        <v>7183164</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515954</v>
+        <v>121515930</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594162</v>
+        <v>593799</v>
       </c>
       <c r="R7" t="n">
-        <v>7182918</v>
+        <v>7183160</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515938</v>
+        <v>121515954</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,39 +1382,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593866</v>
+        <v>594162</v>
       </c>
       <c r="R8" t="n">
-        <v>7183116</v>
+        <v>7182918</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515953</v>
+        <v>121515928</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,7 +1514,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594162</v>
+        <v>593793</v>
       </c>
       <c r="R9" t="n">
-        <v>7182917</v>
+        <v>7183160</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515924</v>
+        <v>121515923</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1611,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593759</v>
+        <v>593761</v>
       </c>
       <c r="R10" t="n">
         <v>7183183</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515928</v>
+        <v>121515939</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593793</v>
+        <v>593874</v>
       </c>
       <c r="R11" t="n">
-        <v>7183160</v>
+        <v>7183112</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515929</v>
+        <v>121515943</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,39 +1845,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593799</v>
+        <v>593939</v>
       </c>
       <c r="R12" t="n">
-        <v>7183161</v>
+        <v>7183054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515923</v>
+        <v>121515937</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,39 +1957,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593761</v>
+        <v>593844</v>
       </c>
       <c r="R13" t="n">
-        <v>7183183</v>
+        <v>7183109</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515942</v>
+        <v>121515941</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,39 +2069,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593940</v>
+        <v>593896</v>
       </c>
       <c r="R14" t="n">
-        <v>7183055</v>
+        <v>7183092</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2143,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515930</v>
+        <v>121515935</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,34 +2181,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593799</v>
+        <v>593842</v>
       </c>
       <c r="R15" t="n">
-        <v>7183160</v>
+        <v>7183114</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2255,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515932</v>
+        <v>121515938</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,34 +2298,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593807</v>
+        <v>593866</v>
       </c>
       <c r="R16" t="n">
-        <v>7183156</v>
+        <v>7183116</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2367,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515944</v>
+        <v>121515926</v>
       </c>
       <c r="B17" t="n">
-        <v>77545</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,34 +2415,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593959</v>
+        <v>593785</v>
       </c>
       <c r="R17" t="n">
-        <v>7183054</v>
+        <v>7183163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515937</v>
+        <v>121515934</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593844</v>
+        <v>593840</v>
       </c>
       <c r="R18" t="n">
-        <v>7183109</v>
+        <v>7183113</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515933</v>
+        <v>121515932</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2644,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593834</v>
+        <v>593807</v>
       </c>
       <c r="R19" t="n">
-        <v>7183112</v>
+        <v>7183156</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515949</v>
+        <v>121515951</v>
       </c>
       <c r="B20" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2756,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2785,7 +2780,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594135</v>
+        <v>594136</v>
       </c>
       <c r="R20" t="n">
         <v>7182928</v>
@@ -2857,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515935</v>
+        <v>121515947</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>74715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,39 +2868,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593842</v>
+        <v>593958</v>
       </c>
       <c r="R21" t="n">
-        <v>7183114</v>
+        <v>7183049</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515948</v>
+        <v>121515942</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,34 +2980,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593958</v>
+        <v>593940</v>
       </c>
       <c r="R22" t="n">
-        <v>7183050</v>
+        <v>7183055</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3054,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515939</v>
+        <v>121515924</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,39 +3097,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593874</v>
+        <v>593759</v>
       </c>
       <c r="R23" t="n">
-        <v>7183112</v>
+        <v>7183183</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3166,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,7 +3196,7 @@
         <v>121515931</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3320,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515941</v>
+        <v>121515944</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>77546</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3326,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3360,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593896</v>
+        <v>593959</v>
       </c>
       <c r="R25" t="n">
-        <v>7183092</v>
+        <v>7183054</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3395,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,10 +3422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515940</v>
+        <v>121515953</v>
       </c>
       <c r="B26" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,34 +3438,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593895</v>
+        <v>594162</v>
       </c>
       <c r="R26" t="n">
-        <v>7183091</v>
+        <v>7182917</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3507,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515934</v>
+        <v>121515946</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,21 +3555,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593840</v>
+        <v>593959</v>
       </c>
       <c r="R27" t="n">
-        <v>7183113</v>
+        <v>7183052</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3619,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515927</v>
+        <v>121515933</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,34 +3667,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593785</v>
+        <v>593834</v>
       </c>
       <c r="R28" t="n">
-        <v>7183164</v>
+        <v>7183112</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515946</v>
+        <v>121515949</v>
       </c>
       <c r="B29" t="n">
-        <v>82392</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593959</v>
+        <v>594135</v>
       </c>
       <c r="R29" t="n">
-        <v>7183052</v>
+        <v>7182928</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515951</v>
+        <v>121515936</v>
       </c>
       <c r="B30" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594136</v>
+        <v>593845</v>
       </c>
       <c r="R30" t="n">
-        <v>7182928</v>
+        <v>7183110</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515940</v>
+        <v>121515947</v>
       </c>
       <c r="B3" t="n">
-        <v>82393</v>
+        <v>74715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593895</v>
+        <v>593958</v>
       </c>
       <c r="R3" t="n">
-        <v>7183091</v>
+        <v>7183049</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515929</v>
+        <v>121515943</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593799</v>
+        <v>593939</v>
       </c>
       <c r="R4" t="n">
-        <v>7183161</v>
+        <v>7183054</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515948</v>
+        <v>121515951</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1070,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593958</v>
+        <v>594136</v>
       </c>
       <c r="R5" t="n">
-        <v>7183050</v>
+        <v>7182928</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515927</v>
+        <v>121515942</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593785</v>
+        <v>593940</v>
       </c>
       <c r="R6" t="n">
-        <v>7183164</v>
+        <v>7183055</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515930</v>
+        <v>121515928</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,31 +1270,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593799</v>
+        <v>593793</v>
       </c>
       <c r="R7" t="n">
         <v>7183160</v>
@@ -1366,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515954</v>
+        <v>121515946</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594162</v>
+        <v>593959</v>
       </c>
       <c r="R8" t="n">
-        <v>7182918</v>
+        <v>7183052</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515928</v>
+        <v>121515948</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593793</v>
+        <v>593958</v>
       </c>
       <c r="R9" t="n">
-        <v>7183160</v>
+        <v>7183050</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515923</v>
+        <v>121515927</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593761</v>
+        <v>593785</v>
       </c>
       <c r="R10" t="n">
-        <v>7183183</v>
+        <v>7183164</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515939</v>
+        <v>121515924</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593874</v>
+        <v>593759</v>
       </c>
       <c r="R11" t="n">
-        <v>7183112</v>
+        <v>7183183</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515943</v>
+        <v>121515930</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1869,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593939</v>
+        <v>593799</v>
       </c>
       <c r="R12" t="n">
-        <v>7183054</v>
+        <v>7183160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515941</v>
+        <v>121515939</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2059,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593896</v>
+        <v>593874</v>
       </c>
       <c r="R14" t="n">
-        <v>7183092</v>
+        <v>7183112</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2160,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515935</v>
+        <v>121515923</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2201,7 +2196,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593842</v>
+        <v>593761</v>
       </c>
       <c r="R15" t="n">
-        <v>7183114</v>
+        <v>7183183</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515938</v>
+        <v>121515940</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,39 +2293,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593866</v>
+        <v>593895</v>
       </c>
       <c r="R16" t="n">
-        <v>7183116</v>
+        <v>7183091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515926</v>
+        <v>121515936</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,39 +2405,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593785</v>
+        <v>593845</v>
       </c>
       <c r="R17" t="n">
-        <v>7183163</v>
+        <v>7183110</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,7 +2501,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515934</v>
+        <v>121515932</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2556,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593840</v>
+        <v>593807</v>
       </c>
       <c r="R18" t="n">
-        <v>7183113</v>
+        <v>7183156</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,7 +2613,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515932</v>
+        <v>121515954</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2668,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593807</v>
+        <v>594162</v>
       </c>
       <c r="R19" t="n">
-        <v>7183156</v>
+        <v>7182918</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,7 +2725,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515951</v>
+        <v>121515934</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2780,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594136</v>
+        <v>593840</v>
       </c>
       <c r="R20" t="n">
-        <v>7182928</v>
+        <v>7183113</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515947</v>
+        <v>121515944</v>
       </c>
       <c r="B21" t="n">
-        <v>74715</v>
+        <v>77546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,21 +2853,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593958</v>
+        <v>593959</v>
       </c>
       <c r="R21" t="n">
-        <v>7183049</v>
+        <v>7183054</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2964,7 +2949,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515942</v>
+        <v>121515931</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -3000,7 +2985,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3009,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593940</v>
+        <v>593808</v>
       </c>
       <c r="R22" t="n">
-        <v>7183055</v>
+        <v>7183154</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3044,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515924</v>
+        <v>121515933</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,34 +3082,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593759</v>
+        <v>593834</v>
       </c>
       <c r="R23" t="n">
-        <v>7183183</v>
+        <v>7183112</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,7 +3183,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515931</v>
+        <v>121515953</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3229,7 +3219,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3238,10 +3228,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593808</v>
+        <v>594162</v>
       </c>
       <c r="R24" t="n">
-        <v>7183154</v>
+        <v>7182917</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515944</v>
+        <v>121515938</v>
       </c>
       <c r="B25" t="n">
-        <v>77546</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,34 +3316,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593959</v>
+        <v>593866</v>
       </c>
       <c r="R25" t="n">
-        <v>7183054</v>
+        <v>7183116</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3390,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515953</v>
+        <v>121515949</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,39 +3433,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594162</v>
+        <v>594135</v>
       </c>
       <c r="R26" t="n">
-        <v>7182917</v>
+        <v>7182928</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3502,7 +3492,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3502,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515946</v>
+        <v>121515941</v>
       </c>
       <c r="B27" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3555,21 +3545,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3579,10 +3569,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593959</v>
+        <v>593896</v>
       </c>
       <c r="R27" t="n">
-        <v>7183052</v>
+        <v>7183092</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3614,7 +3604,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3614,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,7 +3641,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515933</v>
+        <v>121515926</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3696,10 +3686,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593834</v>
+        <v>593785</v>
       </c>
       <c r="R28" t="n">
-        <v>7183112</v>
+        <v>7183163</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3731,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515949</v>
+        <v>121515929</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,34 +3774,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594135</v>
+        <v>593799</v>
       </c>
       <c r="R29" t="n">
-        <v>7182928</v>
+        <v>7183161</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515936</v>
+        <v>121515935</v>
       </c>
       <c r="B30" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,34 +3891,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593845</v>
+        <v>593842</v>
       </c>
       <c r="R30" t="n">
-        <v>7183110</v>
+        <v>7183114</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515947</v>
+        <v>121515931</v>
       </c>
       <c r="B3" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593958</v>
+        <v>593808</v>
       </c>
       <c r="R3" t="n">
-        <v>7183049</v>
+        <v>7183154</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515943</v>
+        <v>121515951</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -953,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593939</v>
+        <v>594136</v>
       </c>
       <c r="R4" t="n">
-        <v>7183054</v>
+        <v>7182928</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515951</v>
+        <v>121515926</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1046,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594136</v>
+        <v>593785</v>
       </c>
       <c r="R5" t="n">
-        <v>7182928</v>
+        <v>7183163</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515942</v>
+        <v>121515923</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1182,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593940</v>
+        <v>593761</v>
       </c>
       <c r="R6" t="n">
-        <v>7183055</v>
+        <v>7183183</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515928</v>
+        <v>121515943</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593793</v>
+        <v>593939</v>
       </c>
       <c r="R7" t="n">
-        <v>7183160</v>
+        <v>7183054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515946</v>
+        <v>121515954</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R8" t="n">
-        <v>7183052</v>
+        <v>7182918</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515948</v>
+        <v>121515949</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593958</v>
+        <v>594135</v>
       </c>
       <c r="R9" t="n">
-        <v>7183050</v>
+        <v>7182928</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515927</v>
+        <v>121515929</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593785</v>
+        <v>593799</v>
       </c>
       <c r="R10" t="n">
-        <v>7183164</v>
+        <v>7183161</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515924</v>
+        <v>121515935</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,34 +1733,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593759</v>
+        <v>593842</v>
       </c>
       <c r="R11" t="n">
-        <v>7183183</v>
+        <v>7183114</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,7 +1834,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515930</v>
+        <v>121515924</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1859,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593799</v>
+        <v>593759</v>
       </c>
       <c r="R12" t="n">
-        <v>7183160</v>
+        <v>7183183</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515937</v>
+        <v>121515928</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,34 +1962,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593844</v>
+        <v>593793</v>
       </c>
       <c r="R13" t="n">
-        <v>7183109</v>
+        <v>7183160</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515939</v>
+        <v>121515933</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2088,7 +2108,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593874</v>
+        <v>593834</v>
       </c>
       <c r="R14" t="n">
         <v>7183112</v>
@@ -2123,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515923</v>
+        <v>121515946</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,39 +2196,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593761</v>
+        <v>593959</v>
       </c>
       <c r="R15" t="n">
-        <v>7183183</v>
+        <v>7183052</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515940</v>
+        <v>121515930</v>
       </c>
       <c r="B16" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,21 +2308,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593895</v>
+        <v>593799</v>
       </c>
       <c r="R16" t="n">
-        <v>7183091</v>
+        <v>7183160</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515936</v>
+        <v>121515942</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,34 +2420,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593845</v>
+        <v>593940</v>
       </c>
       <c r="R17" t="n">
-        <v>7183110</v>
+        <v>7183055</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2464,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515932</v>
+        <v>121515948</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2541,10 +2561,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593807</v>
+        <v>593958</v>
       </c>
       <c r="R18" t="n">
-        <v>7183156</v>
+        <v>7183050</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515954</v>
+        <v>121515934</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2653,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594162</v>
+        <v>593840</v>
       </c>
       <c r="R19" t="n">
-        <v>7182918</v>
+        <v>7183113</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515934</v>
+        <v>121515937</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2765,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593840</v>
+        <v>593844</v>
       </c>
       <c r="R20" t="n">
-        <v>7183113</v>
+        <v>7183109</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515944</v>
+        <v>121515953</v>
       </c>
       <c r="B21" t="n">
-        <v>77546</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,34 +2873,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R21" t="n">
-        <v>7183054</v>
+        <v>7182917</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2912,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,7 +2974,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515931</v>
+        <v>121515939</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2994,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593808</v>
+        <v>593874</v>
       </c>
       <c r="R22" t="n">
-        <v>7183154</v>
+        <v>7183112</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3029,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515933</v>
+        <v>121515941</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3082,39 +3107,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593834</v>
+        <v>593896</v>
       </c>
       <c r="R23" t="n">
-        <v>7183112</v>
+        <v>7183092</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515953</v>
+        <v>121515940</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,39 +3219,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594162</v>
+        <v>593895</v>
       </c>
       <c r="R24" t="n">
-        <v>7182917</v>
+        <v>7183091</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3263,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,10 +3315,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515938</v>
+        <v>121515944</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>77546</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,39 +3331,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593866</v>
+        <v>593959</v>
       </c>
       <c r="R25" t="n">
-        <v>7183116</v>
+        <v>7183054</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3380,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,10 +3427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515949</v>
+        <v>121515947</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>74715</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3433,21 +3443,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3457,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594135</v>
+        <v>593958</v>
       </c>
       <c r="R26" t="n">
-        <v>7182928</v>
+        <v>7183049</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3492,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3502,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,7 +3539,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515941</v>
+        <v>121515927</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3569,10 +3579,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593896</v>
+        <v>593785</v>
       </c>
       <c r="R27" t="n">
-        <v>7183092</v>
+        <v>7183164</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3604,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3614,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3641,10 +3651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515926</v>
+        <v>121515932</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3657,39 +3667,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593785</v>
+        <v>593807</v>
       </c>
       <c r="R28" t="n">
-        <v>7183163</v>
+        <v>7183156</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,10 +3763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515929</v>
+        <v>121515936</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3774,39 +3779,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593799</v>
+        <v>593845</v>
       </c>
       <c r="R29" t="n">
-        <v>7183161</v>
+        <v>7183110</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,7 +3875,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515935</v>
+        <v>121515938</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593842</v>
+        <v>593866</v>
       </c>
       <c r="R30" t="n">
-        <v>7183114</v>
+        <v>7183116</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515931</v>
+        <v>121515925</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -837,7 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593808</v>
+        <v>593785</v>
       </c>
       <c r="R3" t="n">
-        <v>7183154</v>
+        <v>7183163</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515951</v>
+        <v>121515938</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +934,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594136</v>
+        <v>593866</v>
       </c>
       <c r="R4" t="n">
-        <v>7182928</v>
+        <v>7183116</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515926</v>
+        <v>121515935</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1075,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593785</v>
+        <v>593842</v>
       </c>
       <c r="R5" t="n">
-        <v>7183163</v>
+        <v>7183114</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515923</v>
+        <v>121515936</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593761</v>
+        <v>593845</v>
       </c>
       <c r="R6" t="n">
-        <v>7183183</v>
+        <v>7183110</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515943</v>
+        <v>121515937</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593939</v>
+        <v>593844</v>
       </c>
       <c r="R7" t="n">
-        <v>7183054</v>
+        <v>7183109</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515954</v>
+        <v>121515951</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594162</v>
+        <v>594136</v>
       </c>
       <c r="R8" t="n">
-        <v>7182918</v>
+        <v>7182928</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515949</v>
+        <v>121515929</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594135</v>
+        <v>593799</v>
       </c>
       <c r="R9" t="n">
-        <v>7182928</v>
+        <v>7183161</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1605,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515929</v>
+        <v>121515942</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1645,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593799</v>
+        <v>593940</v>
       </c>
       <c r="R10" t="n">
-        <v>7183161</v>
+        <v>7183055</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515935</v>
+        <v>121515949</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,39 +1738,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593842</v>
+        <v>594135</v>
       </c>
       <c r="R11" t="n">
-        <v>7183114</v>
+        <v>7182928</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1834,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515924</v>
+        <v>121515943</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593759</v>
+        <v>593939</v>
       </c>
       <c r="R12" t="n">
-        <v>7183183</v>
+        <v>7183054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515933</v>
+        <v>121515953</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2099,7 +2099,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593834</v>
+        <v>594162</v>
       </c>
       <c r="R14" t="n">
-        <v>7183112</v>
+        <v>7182917</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515946</v>
+        <v>121515954</v>
       </c>
       <c r="B15" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,21 +2196,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R15" t="n">
-        <v>7183052</v>
+        <v>7182918</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,7 +2292,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515930</v>
+        <v>121515934</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593799</v>
+        <v>593840</v>
       </c>
       <c r="R16" t="n">
-        <v>7183160</v>
+        <v>7183113</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515942</v>
+        <v>121515930</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,39 +2420,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593940</v>
+        <v>593799</v>
       </c>
       <c r="R17" t="n">
-        <v>7183055</v>
+        <v>7183160</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2484,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515948</v>
+        <v>121515947</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,21 +2532,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2564,7 +2559,7 @@
         <v>593958</v>
       </c>
       <c r="R18" t="n">
-        <v>7183050</v>
+        <v>7183049</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2633,7 +2628,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515934</v>
+        <v>121515924</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593840</v>
+        <v>593759</v>
       </c>
       <c r="R19" t="n">
-        <v>7183113</v>
+        <v>7183183</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515937</v>
+        <v>121515946</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2756,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2785,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593844</v>
+        <v>593959</v>
       </c>
       <c r="R20" t="n">
-        <v>7183109</v>
+        <v>7183052</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2820,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515953</v>
+        <v>121515932</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,39 +2868,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594162</v>
+        <v>593807</v>
       </c>
       <c r="R21" t="n">
-        <v>7182917</v>
+        <v>7183156</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515939</v>
+        <v>121515948</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,39 +2980,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593874</v>
+        <v>593958</v>
       </c>
       <c r="R22" t="n">
-        <v>7183112</v>
+        <v>7183050</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3054,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515941</v>
+        <v>121515923</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,34 +3092,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593896</v>
+        <v>593761</v>
       </c>
       <c r="R23" t="n">
-        <v>7183092</v>
+        <v>7183183</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3166,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515940</v>
+        <v>121515931</v>
       </c>
       <c r="B24" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,34 +3209,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593895</v>
+        <v>593808</v>
       </c>
       <c r="R24" t="n">
-        <v>7183091</v>
+        <v>7183154</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3278,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515944</v>
+        <v>121515933</v>
       </c>
       <c r="B25" t="n">
-        <v>77546</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,34 +3326,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593959</v>
+        <v>593834</v>
       </c>
       <c r="R25" t="n">
-        <v>7183054</v>
+        <v>7183112</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515947</v>
+        <v>121515944</v>
       </c>
       <c r="B26" t="n">
-        <v>74715</v>
+        <v>77546</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593958</v>
+        <v>593959</v>
       </c>
       <c r="R26" t="n">
-        <v>7183049</v>
+        <v>7183054</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515932</v>
+        <v>121515939</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3667,34 +3667,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593807</v>
+        <v>593874</v>
       </c>
       <c r="R28" t="n">
-        <v>7183156</v>
+        <v>7183112</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515936</v>
+        <v>121515940</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593845</v>
+        <v>593895</v>
       </c>
       <c r="R29" t="n">
-        <v>7183110</v>
+        <v>7183091</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515938</v>
+        <v>121515941</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3891,39 +3896,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593866</v>
+        <v>593896</v>
       </c>
       <c r="R30" t="n">
-        <v>7183116</v>
+        <v>7183092</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515926</v>
+        <v>121515934</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593785</v>
+        <v>593840</v>
       </c>
       <c r="R3" t="n">
-        <v>7183163</v>
+        <v>7183113</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515935</v>
+        <v>121515927</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593842</v>
+        <v>593785</v>
       </c>
       <c r="R4" t="n">
-        <v>7183114</v>
+        <v>7183164</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515949</v>
+        <v>121515944</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>77553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594135</v>
+        <v>593959</v>
       </c>
       <c r="R5" t="n">
-        <v>7182928</v>
+        <v>7183054</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515948</v>
+        <v>121515951</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1187,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593958</v>
+        <v>594136</v>
       </c>
       <c r="R6" t="n">
-        <v>7183050</v>
+        <v>7182928</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515934</v>
+        <v>121515923</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593840</v>
+        <v>593761</v>
       </c>
       <c r="R7" t="n">
-        <v>7183113</v>
+        <v>7183183</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515946</v>
+        <v>121515939</v>
       </c>
       <c r="B8" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1382,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593959</v>
+        <v>593874</v>
       </c>
       <c r="R8" t="n">
-        <v>7183052</v>
+        <v>7183112</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515938</v>
+        <v>121515933</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593866</v>
+        <v>593834</v>
       </c>
       <c r="R9" t="n">
-        <v>7183116</v>
+        <v>7183112</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515942</v>
+        <v>121515943</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1616,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593940</v>
+        <v>593939</v>
       </c>
       <c r="R10" t="n">
-        <v>7183055</v>
+        <v>7183054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1717,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515928</v>
+        <v>121515949</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,39 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593793</v>
+        <v>594135</v>
       </c>
       <c r="R11" t="n">
-        <v>7183160</v>
+        <v>7182928</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515937</v>
+        <v>121515924</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1874,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593844</v>
+        <v>593759</v>
       </c>
       <c r="R12" t="n">
-        <v>7183109</v>
+        <v>7183183</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515924</v>
+        <v>121515925</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,34 +1952,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593759</v>
+        <v>593785</v>
       </c>
       <c r="R13" t="n">
-        <v>7183183</v>
+        <v>7183163</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,7 +2053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515927</v>
+        <v>121515948</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593785</v>
+        <v>593958</v>
       </c>
       <c r="R14" t="n">
-        <v>7183164</v>
+        <v>7183050</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515932</v>
+        <v>121515930</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593807</v>
+        <v>593799</v>
       </c>
       <c r="R15" t="n">
-        <v>7183156</v>
+        <v>7183160</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515929</v>
+        <v>121515931</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2318,7 +2313,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2327,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593799</v>
+        <v>593808</v>
       </c>
       <c r="R16" t="n">
-        <v>7183161</v>
+        <v>7183154</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,7 +2394,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515939</v>
+        <v>121515935</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593874</v>
+        <v>593842</v>
       </c>
       <c r="R17" t="n">
-        <v>7183112</v>
+        <v>7183114</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515951</v>
+        <v>121515946</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594136</v>
+        <v>593959</v>
       </c>
       <c r="R18" t="n">
-        <v>7182928</v>
+        <v>7183052</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515944</v>
+        <v>121515928</v>
       </c>
       <c r="B19" t="n">
-        <v>77553</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2639,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593959</v>
+        <v>593793</v>
       </c>
       <c r="R19" t="n">
-        <v>7183054</v>
+        <v>7183160</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515940</v>
+        <v>121515954</v>
       </c>
       <c r="B20" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,21 +2756,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593895</v>
+        <v>594162</v>
       </c>
       <c r="R20" t="n">
-        <v>7183091</v>
+        <v>7182918</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,7 +2852,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515933</v>
+        <v>121515929</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2888,7 +2888,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593834</v>
+        <v>593799</v>
       </c>
       <c r="R21" t="n">
-        <v>7183112</v>
+        <v>7183161</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515941</v>
+        <v>121515942</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,34 +2985,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593896</v>
+        <v>593940</v>
       </c>
       <c r="R22" t="n">
-        <v>7183092</v>
+        <v>7183055</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3044,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515947</v>
+        <v>121515940</v>
       </c>
       <c r="B23" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,21 +3102,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593958</v>
+        <v>593895</v>
       </c>
       <c r="R23" t="n">
-        <v>7183049</v>
+        <v>7183091</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515931</v>
+        <v>121515941</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,39 +3214,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593808</v>
+        <v>593896</v>
       </c>
       <c r="R24" t="n">
-        <v>7183154</v>
+        <v>7183092</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515923</v>
+        <v>121515947</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,39 +3326,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593761</v>
+        <v>593958</v>
       </c>
       <c r="R25" t="n">
-        <v>7183183</v>
+        <v>7183049</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3390,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,10 +3422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515936</v>
+        <v>121515932</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593845</v>
+        <v>593807</v>
       </c>
       <c r="R26" t="n">
-        <v>7183110</v>
+        <v>7183156</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3502,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515943</v>
+        <v>121515938</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3555,34 +3550,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593939</v>
+        <v>593866</v>
       </c>
       <c r="R27" t="n">
-        <v>7183054</v>
+        <v>7183116</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515930</v>
+        <v>121515937</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593799</v>
+        <v>593844</v>
       </c>
       <c r="R29" t="n">
-        <v>7183160</v>
+        <v>7183109</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515954</v>
+        <v>121515936</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594162</v>
+        <v>593845</v>
       </c>
       <c r="R30" t="n">
-        <v>7182918</v>
+        <v>7183110</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -2969,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515942</v>
+        <v>121515940</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,39 +2985,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593940</v>
+        <v>593895</v>
       </c>
       <c r="R22" t="n">
-        <v>7183055</v>
+        <v>7183091</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3054,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515940</v>
+        <v>121515941</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,21 +3097,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593895</v>
+        <v>593896</v>
       </c>
       <c r="R23" t="n">
-        <v>7183091</v>
+        <v>7183092</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515941</v>
+        <v>121515947</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,21 +3209,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593896</v>
+        <v>593958</v>
       </c>
       <c r="R24" t="n">
-        <v>7183092</v>
+        <v>7183049</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515947</v>
+        <v>121515942</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,34 +3321,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593958</v>
+        <v>593940</v>
       </c>
       <c r="R25" t="n">
-        <v>7183049</v>
+        <v>7183055</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515934</v>
+        <v>121515947</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593840</v>
+        <v>593958</v>
       </c>
       <c r="R3" t="n">
-        <v>7183113</v>
+        <v>7183049</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515927</v>
+        <v>121515941</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593785</v>
+        <v>593896</v>
       </c>
       <c r="R4" t="n">
-        <v>7183164</v>
+        <v>7183092</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515944</v>
+        <v>121515951</v>
       </c>
       <c r="B5" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593959</v>
+        <v>594136</v>
       </c>
       <c r="R5" t="n">
-        <v>7183054</v>
+        <v>7182928</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515951</v>
+        <v>121515944</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>77553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594136</v>
+        <v>593959</v>
       </c>
       <c r="R6" t="n">
-        <v>7182928</v>
+        <v>7183054</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515923</v>
+        <v>121515930</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593761</v>
+        <v>593799</v>
       </c>
       <c r="R7" t="n">
-        <v>7183183</v>
+        <v>7183160</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515939</v>
+        <v>121515931</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1411,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593874</v>
+        <v>593808</v>
       </c>
       <c r="R8" t="n">
-        <v>7183112</v>
+        <v>7183154</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515933</v>
+        <v>121515949</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593834</v>
+        <v>594135</v>
       </c>
       <c r="R9" t="n">
-        <v>7183112</v>
+        <v>7182928</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515943</v>
+        <v>121515934</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1640,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593939</v>
+        <v>593840</v>
       </c>
       <c r="R10" t="n">
-        <v>7183054</v>
+        <v>7183113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515949</v>
+        <v>121515935</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594135</v>
+        <v>593842</v>
       </c>
       <c r="R11" t="n">
-        <v>7182928</v>
+        <v>7183114</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515924</v>
+        <v>121515948</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1864,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593759</v>
+        <v>593958</v>
       </c>
       <c r="R12" t="n">
-        <v>7183183</v>
+        <v>7183050</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,7 +2048,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515948</v>
+        <v>121515927</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593958</v>
+        <v>593785</v>
       </c>
       <c r="R14" t="n">
-        <v>7183050</v>
+        <v>7183164</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2160,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515930</v>
+        <v>121515943</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2205,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593799</v>
+        <v>593939</v>
       </c>
       <c r="R15" t="n">
-        <v>7183160</v>
+        <v>7183054</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,7 +2272,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515931</v>
+        <v>121515923</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2313,7 +2308,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593808</v>
+        <v>593761</v>
       </c>
       <c r="R16" t="n">
-        <v>7183154</v>
+        <v>7183183</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,7 +2389,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515935</v>
+        <v>121515942</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2430,7 +2425,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593842</v>
+        <v>593940</v>
       </c>
       <c r="R17" t="n">
-        <v>7183114</v>
+        <v>7183055</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515946</v>
+        <v>121515929</v>
       </c>
       <c r="B18" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,34 +2522,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593959</v>
+        <v>593799</v>
       </c>
       <c r="R18" t="n">
-        <v>7183052</v>
+        <v>7183161</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515928</v>
+        <v>121515940</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,39 +2639,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593793</v>
+        <v>593895</v>
       </c>
       <c r="R19" t="n">
-        <v>7183160</v>
+        <v>7183091</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515929</v>
+        <v>121515936</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,39 +2863,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593799</v>
+        <v>593845</v>
       </c>
       <c r="R21" t="n">
-        <v>7183161</v>
+        <v>7183110</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2932,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515940</v>
+        <v>121515953</v>
       </c>
       <c r="B22" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,34 +2975,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593895</v>
+        <v>594162</v>
       </c>
       <c r="R22" t="n">
-        <v>7183091</v>
+        <v>7182917</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3044,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515941</v>
+        <v>121515946</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,21 +3092,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3121,10 +3116,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593896</v>
+        <v>593959</v>
       </c>
       <c r="R23" t="n">
-        <v>7183092</v>
+        <v>7183052</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515947</v>
+        <v>121515938</v>
       </c>
       <c r="B24" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,34 +3204,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593958</v>
+        <v>593866</v>
       </c>
       <c r="R24" t="n">
-        <v>7183049</v>
+        <v>7183116</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515942</v>
+        <v>121515939</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3341,7 +3341,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593940</v>
+        <v>593874</v>
       </c>
       <c r="R25" t="n">
-        <v>7183055</v>
+        <v>7183112</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,7 +3422,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515932</v>
+        <v>121515924</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593807</v>
+        <v>593759</v>
       </c>
       <c r="R26" t="n">
-        <v>7183156</v>
+        <v>7183183</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515938</v>
+        <v>121515933</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593866</v>
+        <v>593834</v>
       </c>
       <c r="R27" t="n">
-        <v>7183116</v>
+        <v>7183112</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515953</v>
+        <v>121515937</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3667,39 +3667,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594162</v>
+        <v>593844</v>
       </c>
       <c r="R28" t="n">
-        <v>7182917</v>
+        <v>7183109</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,7 +3763,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515937</v>
+        <v>121515932</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593844</v>
+        <v>593807</v>
       </c>
       <c r="R29" t="n">
-        <v>7183109</v>
+        <v>7183156</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3875,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515936</v>
+        <v>121515928</v>
       </c>
       <c r="B30" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,34 +3891,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593845</v>
+        <v>593793</v>
       </c>
       <c r="R30" t="n">
-        <v>7183110</v>
+        <v>7183160</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515930</v>
+        <v>121515949</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593799</v>
+        <v>594135</v>
       </c>
       <c r="R7" t="n">
-        <v>7183160</v>
+        <v>7182928</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515931</v>
+        <v>121515930</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593808</v>
+        <v>593799</v>
       </c>
       <c r="R8" t="n">
-        <v>7183154</v>
+        <v>7183160</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515949</v>
+        <v>121515931</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594135</v>
+        <v>593808</v>
       </c>
       <c r="R9" t="n">
-        <v>7182928</v>
+        <v>7183154</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515953</v>
+        <v>121515946</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,39 +2975,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594162</v>
+        <v>593959</v>
       </c>
       <c r="R22" t="n">
-        <v>7182917</v>
+        <v>7183052</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3039,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515946</v>
+        <v>121515953</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,34 +3087,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R23" t="n">
-        <v>7183052</v>
+        <v>7182917</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515947</v>
+        <v>121515946</v>
       </c>
       <c r="B3" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593958</v>
+        <v>593959</v>
       </c>
       <c r="R3" t="n">
-        <v>7183049</v>
+        <v>7183052</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515941</v>
+        <v>121515936</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593896</v>
+        <v>593845</v>
       </c>
       <c r="R4" t="n">
-        <v>7183092</v>
+        <v>7183110</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515951</v>
+        <v>121515941</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594136</v>
+        <v>593896</v>
       </c>
       <c r="R5" t="n">
-        <v>7182928</v>
+        <v>7183092</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515944</v>
+        <v>121515932</v>
       </c>
       <c r="B6" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593959</v>
+        <v>593807</v>
       </c>
       <c r="R6" t="n">
-        <v>7183054</v>
+        <v>7183156</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515949</v>
+        <v>121515931</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594135</v>
+        <v>593808</v>
       </c>
       <c r="R7" t="n">
-        <v>7182928</v>
+        <v>7183154</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515930</v>
+        <v>121515926</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1382,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593799</v>
+        <v>593785</v>
       </c>
       <c r="R8" t="n">
-        <v>7183160</v>
+        <v>7183163</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515931</v>
+        <v>121515934</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593808</v>
+        <v>593840</v>
       </c>
       <c r="R9" t="n">
-        <v>7183154</v>
+        <v>7183113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515934</v>
+        <v>121515954</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1630,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593840</v>
+        <v>594162</v>
       </c>
       <c r="R10" t="n">
-        <v>7183113</v>
+        <v>7182918</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515935</v>
+        <v>121515948</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593842</v>
+        <v>593958</v>
       </c>
       <c r="R11" t="n">
-        <v>7183114</v>
+        <v>7183050</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515948</v>
+        <v>121515939</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,34 +1835,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593958</v>
+        <v>593874</v>
       </c>
       <c r="R12" t="n">
-        <v>7183050</v>
+        <v>7183112</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515925</v>
+        <v>121515949</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,39 +1952,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593785</v>
+        <v>594135</v>
       </c>
       <c r="R13" t="n">
-        <v>7183163</v>
+        <v>7182928</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515927</v>
+        <v>121515929</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,34 +2064,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593785</v>
+        <v>593799</v>
       </c>
       <c r="R14" t="n">
-        <v>7183164</v>
+        <v>7183161</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515943</v>
+        <v>121515923</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,34 +2181,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593939</v>
+        <v>593761</v>
       </c>
       <c r="R15" t="n">
-        <v>7183054</v>
+        <v>7183183</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,7 +2282,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515923</v>
+        <v>121515938</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2308,7 +2318,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2317,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593761</v>
+        <v>593866</v>
       </c>
       <c r="R16" t="n">
-        <v>7183183</v>
+        <v>7183116</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515942</v>
+        <v>121515940</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,39 +2415,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593940</v>
+        <v>593895</v>
       </c>
       <c r="R17" t="n">
-        <v>7183055</v>
+        <v>7183091</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515929</v>
+        <v>121515937</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,39 +2527,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593799</v>
+        <v>593844</v>
       </c>
       <c r="R18" t="n">
-        <v>7183161</v>
+        <v>7183109</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515940</v>
+        <v>121515924</v>
       </c>
       <c r="B19" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593895</v>
+        <v>593759</v>
       </c>
       <c r="R19" t="n">
-        <v>7183091</v>
+        <v>7183183</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,7 +2735,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515954</v>
+        <v>121515930</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594162</v>
+        <v>593799</v>
       </c>
       <c r="R20" t="n">
-        <v>7182918</v>
+        <v>7183160</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515936</v>
+        <v>121515953</v>
       </c>
       <c r="B21" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,34 +2863,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593845</v>
+        <v>594162</v>
       </c>
       <c r="R21" t="n">
-        <v>7183110</v>
+        <v>7182917</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515946</v>
+        <v>121515947</v>
       </c>
       <c r="B22" t="n">
-        <v>82400</v>
+        <v>74722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,21 +2980,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593959</v>
+        <v>593958</v>
       </c>
       <c r="R22" t="n">
-        <v>7183052</v>
+        <v>7183049</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3071,7 +3076,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515953</v>
+        <v>121515942</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594162</v>
+        <v>593940</v>
       </c>
       <c r="R23" t="n">
-        <v>7182917</v>
+        <v>7183055</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3151,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515938</v>
+        <v>121515944</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,39 +3209,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593866</v>
+        <v>593959</v>
       </c>
       <c r="R24" t="n">
-        <v>7183116</v>
+        <v>7183054</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,10 +3305,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515939</v>
+        <v>121515927</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,39 +3321,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593874</v>
+        <v>593785</v>
       </c>
       <c r="R25" t="n">
-        <v>7183112</v>
+        <v>7183164</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3390,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515924</v>
+        <v>121515935</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,34 +3433,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593759</v>
+        <v>593842</v>
       </c>
       <c r="R26" t="n">
-        <v>7183183</v>
+        <v>7183114</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515933</v>
+        <v>121515951</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,39 +3550,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593834</v>
+        <v>594136</v>
       </c>
       <c r="R27" t="n">
-        <v>7183112</v>
+        <v>7182928</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3614,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,7 +3646,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515937</v>
+        <v>121515943</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -3691,10 +3686,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593844</v>
+        <v>593939</v>
       </c>
       <c r="R28" t="n">
-        <v>7183109</v>
+        <v>7183054</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3726,7 +3721,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3731,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515932</v>
+        <v>121515928</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,34 +3774,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593807</v>
+        <v>593793</v>
       </c>
       <c r="R29" t="n">
-        <v>7183156</v>
+        <v>7183160</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,7 +3875,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515928</v>
+        <v>121515933</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593793</v>
+        <v>593834</v>
       </c>
       <c r="R30" t="n">
-        <v>7183160</v>
+        <v>7183112</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515946</v>
+        <v>121515938</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593959</v>
+        <v>593866</v>
       </c>
       <c r="R3" t="n">
-        <v>7183052</v>
+        <v>7183116</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515936</v>
+        <v>121515931</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,34 +934,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593845</v>
+        <v>593808</v>
       </c>
       <c r="R4" t="n">
-        <v>7183110</v>
+        <v>7183154</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515941</v>
+        <v>121515939</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593896</v>
+        <v>593874</v>
       </c>
       <c r="R5" t="n">
-        <v>7183092</v>
+        <v>7183112</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515932</v>
+        <v>121515934</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1177,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593807</v>
+        <v>593840</v>
       </c>
       <c r="R6" t="n">
-        <v>7183156</v>
+        <v>7183113</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515931</v>
+        <v>121515924</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593808</v>
+        <v>593759</v>
       </c>
       <c r="R7" t="n">
-        <v>7183154</v>
+        <v>7183183</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515926</v>
+        <v>121515930</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,39 +1392,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593785</v>
+        <v>593799</v>
       </c>
       <c r="R8" t="n">
-        <v>7183163</v>
+        <v>7183160</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515934</v>
+        <v>121515954</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593840</v>
+        <v>594162</v>
       </c>
       <c r="R9" t="n">
-        <v>7183113</v>
+        <v>7182918</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515954</v>
+        <v>121515926</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594162</v>
+        <v>593785</v>
       </c>
       <c r="R10" t="n">
-        <v>7182918</v>
+        <v>7183163</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515948</v>
+        <v>121515953</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,34 +1733,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593958</v>
+        <v>594162</v>
       </c>
       <c r="R11" t="n">
-        <v>7183050</v>
+        <v>7182917</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515939</v>
+        <v>121515947</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1850,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593874</v>
+        <v>593958</v>
       </c>
       <c r="R12" t="n">
-        <v>7183112</v>
+        <v>7183049</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515949</v>
+        <v>121515929</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,34 +1962,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594135</v>
+        <v>593799</v>
       </c>
       <c r="R13" t="n">
-        <v>7182928</v>
+        <v>7183161</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515929</v>
+        <v>121515948</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,39 +2079,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593799</v>
+        <v>593958</v>
       </c>
       <c r="R14" t="n">
-        <v>7183161</v>
+        <v>7183050</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515923</v>
+        <v>121515941</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,39 +2191,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593761</v>
+        <v>593896</v>
       </c>
       <c r="R15" t="n">
-        <v>7183183</v>
+        <v>7183092</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515938</v>
+        <v>121515936</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,39 +2303,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593866</v>
+        <v>593845</v>
       </c>
       <c r="R16" t="n">
-        <v>7183116</v>
+        <v>7183110</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515940</v>
+        <v>121515942</v>
       </c>
       <c r="B17" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,34 +2415,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593895</v>
+        <v>593940</v>
       </c>
       <c r="R17" t="n">
-        <v>7183091</v>
+        <v>7183055</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515937</v>
+        <v>121515951</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593844</v>
+        <v>594136</v>
       </c>
       <c r="R18" t="n">
-        <v>7183109</v>
+        <v>7182928</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515924</v>
+        <v>121515935</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,34 +2644,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593759</v>
+        <v>593842</v>
       </c>
       <c r="R19" t="n">
-        <v>7183183</v>
+        <v>7183114</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515930</v>
+        <v>121515940</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2775,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593799</v>
+        <v>593895</v>
       </c>
       <c r="R20" t="n">
-        <v>7183160</v>
+        <v>7183091</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515953</v>
+        <v>121515949</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,39 +2873,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594162</v>
+        <v>594135</v>
       </c>
       <c r="R21" t="n">
-        <v>7182917</v>
+        <v>7182928</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2927,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515947</v>
+        <v>121515943</v>
       </c>
       <c r="B22" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,21 +2985,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593958</v>
+        <v>593939</v>
       </c>
       <c r="R22" t="n">
-        <v>7183049</v>
+        <v>7183054</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3039,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3054,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515942</v>
+        <v>121515937</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,39 +3097,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593940</v>
+        <v>593844</v>
       </c>
       <c r="R23" t="n">
-        <v>7183055</v>
+        <v>7183109</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515944</v>
+        <v>121515923</v>
       </c>
       <c r="B24" t="n">
-        <v>77553</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,34 +3209,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593959</v>
+        <v>593761</v>
       </c>
       <c r="R24" t="n">
-        <v>7183054</v>
+        <v>7183183</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3268,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,10 +3422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515935</v>
+        <v>121515944</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3433,39 +3438,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593842</v>
+        <v>593959</v>
       </c>
       <c r="R26" t="n">
-        <v>7183114</v>
+        <v>7183054</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515951</v>
+        <v>121515946</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,21 +3550,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594136</v>
+        <v>593959</v>
       </c>
       <c r="R27" t="n">
-        <v>7182928</v>
+        <v>7183052</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515943</v>
+        <v>121515933</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,34 +3662,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593939</v>
+        <v>593834</v>
       </c>
       <c r="R28" t="n">
-        <v>7183054</v>
+        <v>7183112</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3875,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515933</v>
+        <v>121515932</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3891,39 +3896,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593834</v>
+        <v>593807</v>
       </c>
       <c r="R30" t="n">
-        <v>7183112</v>
+        <v>7183156</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515938</v>
+        <v>121515948</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593866</v>
+        <v>593958</v>
       </c>
       <c r="R3" t="n">
-        <v>7183116</v>
+        <v>7183050</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515931</v>
+        <v>121515938</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593808</v>
+        <v>593866</v>
       </c>
       <c r="R4" t="n">
-        <v>7183154</v>
+        <v>7183116</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515939</v>
+        <v>121515923</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1071,7 +1066,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593874</v>
+        <v>593761</v>
       </c>
       <c r="R5" t="n">
-        <v>7183112</v>
+        <v>7183183</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515934</v>
+        <v>121515939</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593840</v>
+        <v>593874</v>
       </c>
       <c r="R6" t="n">
-        <v>7183113</v>
+        <v>7183112</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515924</v>
+        <v>121515932</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593759</v>
+        <v>593807</v>
       </c>
       <c r="R7" t="n">
-        <v>7183183</v>
+        <v>7183156</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515930</v>
+        <v>121515927</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593799</v>
+        <v>593785</v>
       </c>
       <c r="R8" t="n">
-        <v>7183160</v>
+        <v>7183164</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515954</v>
+        <v>121515929</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594162</v>
+        <v>593799</v>
       </c>
       <c r="R9" t="n">
-        <v>7182918</v>
+        <v>7183161</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515926</v>
+        <v>121515936</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1621,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593785</v>
+        <v>593845</v>
       </c>
       <c r="R10" t="n">
-        <v>7183163</v>
+        <v>7183110</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,7 +1717,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515953</v>
+        <v>121515931</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1753,7 +1753,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594162</v>
+        <v>593808</v>
       </c>
       <c r="R11" t="n">
-        <v>7182917</v>
+        <v>7183154</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515947</v>
+        <v>121515946</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593958</v>
+        <v>593959</v>
       </c>
       <c r="R12" t="n">
-        <v>7183049</v>
+        <v>7183052</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515929</v>
+        <v>121515934</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,39 +1962,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593799</v>
+        <v>593840</v>
       </c>
       <c r="R13" t="n">
-        <v>7183161</v>
+        <v>7183113</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,7 +2058,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515948</v>
+        <v>121515930</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593958</v>
+        <v>593799</v>
       </c>
       <c r="R14" t="n">
-        <v>7183050</v>
+        <v>7183160</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2138,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515941</v>
+        <v>121515943</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593896</v>
+        <v>593939</v>
       </c>
       <c r="R15" t="n">
-        <v>7183092</v>
+        <v>7183054</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2250,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515936</v>
+        <v>121515954</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593845</v>
+        <v>594162</v>
       </c>
       <c r="R16" t="n">
-        <v>7183110</v>
+        <v>7182918</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,7 +2394,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515942</v>
+        <v>121515933</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2435,7 +2430,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593940</v>
+        <v>593834</v>
       </c>
       <c r="R17" t="n">
-        <v>7183055</v>
+        <v>7183112</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515951</v>
+        <v>121515949</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,7 +2551,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594136</v>
+        <v>594135</v>
       </c>
       <c r="R18" t="n">
         <v>7182928</v>
@@ -2628,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515935</v>
+        <v>121515940</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2639,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593842</v>
+        <v>593895</v>
       </c>
       <c r="R19" t="n">
-        <v>7183114</v>
+        <v>7183091</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515940</v>
+        <v>121515925</v>
       </c>
       <c r="B20" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,34 +2751,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593895</v>
+        <v>593785</v>
       </c>
       <c r="R20" t="n">
-        <v>7183091</v>
+        <v>7183163</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2820,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515949</v>
+        <v>121515935</v>
       </c>
       <c r="B21" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,34 +2868,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594135</v>
+        <v>593842</v>
       </c>
       <c r="R21" t="n">
-        <v>7182928</v>
+        <v>7183114</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515943</v>
+        <v>121515942</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,34 +2985,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593939</v>
+        <v>593940</v>
       </c>
       <c r="R22" t="n">
-        <v>7183054</v>
+        <v>7183055</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3081,7 +3086,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515937</v>
+        <v>121515941</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593844</v>
+        <v>593896</v>
       </c>
       <c r="R23" t="n">
-        <v>7183109</v>
+        <v>7183092</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515923</v>
+        <v>121515937</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,39 +3214,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593761</v>
+        <v>593844</v>
       </c>
       <c r="R24" t="n">
-        <v>7183183</v>
+        <v>7183109</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515927</v>
+        <v>121515928</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,34 +3326,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593785</v>
+        <v>593793</v>
       </c>
       <c r="R25" t="n">
-        <v>7183164</v>
+        <v>7183160</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515944</v>
+        <v>121515924</v>
       </c>
       <c r="B26" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,21 +3443,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3462,10 +3467,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593959</v>
+        <v>593759</v>
       </c>
       <c r="R26" t="n">
-        <v>7183054</v>
+        <v>7183183</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515946</v>
+        <v>121515953</v>
       </c>
       <c r="B27" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,34 +3555,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593959</v>
+        <v>594162</v>
       </c>
       <c r="R27" t="n">
-        <v>7183052</v>
+        <v>7182917</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515933</v>
+        <v>121515947</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,39 +3672,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593834</v>
+        <v>593958</v>
       </c>
       <c r="R28" t="n">
-        <v>7183112</v>
+        <v>7183049</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121515928</v>
+        <v>121515944</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,39 +3784,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593793</v>
+        <v>593959</v>
       </c>
       <c r="R29" t="n">
-        <v>7183160</v>
+        <v>7183054</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121515932</v>
+        <v>121515951</v>
       </c>
       <c r="B30" t="n">
         <v>78616</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593807</v>
+        <v>594136</v>
       </c>
       <c r="R30" t="n">
-        <v>7183156</v>
+        <v>7182928</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3990,6 +3990,103 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130881603</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91796</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrbotten, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>594019</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7183022</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Isabelle Holmström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Isabelle Holmström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -3995,7 +3995,7 @@
         <v>130881603</v>
       </c>
       <c r="B31" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 38128-2024 artfynd.xlsx
+++ b/artfynd/A 38128-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56145577</v>
+        <v>121515940</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594108.967967969</v>
+        <v>593895</v>
       </c>
       <c r="R2" t="n">
-        <v>7182941.172639111</v>
+        <v>7183091</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-27</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,45 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515948</v>
+        <v>121515946</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593958</v>
+        <v>593959</v>
       </c>
       <c r="R3" t="n">
-        <v>7183050</v>
+        <v>7183052</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515938</v>
+        <v>121515924</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593866</v>
+        <v>593759</v>
       </c>
       <c r="R4" t="n">
-        <v>7183116</v>
+        <v>7183183</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515923</v>
+        <v>121515927</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593761</v>
+        <v>593785</v>
       </c>
       <c r="R5" t="n">
-        <v>7183183</v>
+        <v>7183164</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,55 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515939</v>
+        <v>121515930</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593874</v>
+        <v>593799</v>
       </c>
       <c r="R6" t="n">
-        <v>7183112</v>
+        <v>7183160</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,16 +1213,11 @@
         <v>121515932</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1376,19 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515927</v>
+        <v>121515934</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1416,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593785</v>
+        <v>593840</v>
       </c>
       <c r="R8" t="n">
-        <v>7183164</v>
+        <v>7183113</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,55 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515929</v>
+        <v>121515937</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593799</v>
+        <v>593844</v>
       </c>
       <c r="R9" t="n">
-        <v>7183161</v>
+        <v>7183109</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515936</v>
+        <v>121515941</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1645,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593845</v>
+        <v>593896</v>
       </c>
       <c r="R10" t="n">
-        <v>7183110</v>
+        <v>7183092</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,55 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515931</v>
+        <v>121515943</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593808</v>
+        <v>593939</v>
       </c>
       <c r="R11" t="n">
-        <v>7183154</v>
+        <v>7183054</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515946</v>
+        <v>121515948</v>
       </c>
       <c r="B12" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593959</v>
+        <v>593958</v>
       </c>
       <c r="R12" t="n">
-        <v>7183052</v>
+        <v>7183050</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1946,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515934</v>
+        <v>121515947</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593840</v>
+        <v>593958</v>
       </c>
       <c r="R13" t="n">
-        <v>7183113</v>
+        <v>7183049</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515930</v>
+        <v>121515923</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +1970,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593799</v>
+        <v>593761</v>
       </c>
       <c r="R14" t="n">
-        <v>7183160</v>
+        <v>7183183</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,15 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515943</v>
+        <v>121515925</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,34 +2082,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593939</v>
+        <v>593785</v>
       </c>
       <c r="R15" t="n">
-        <v>7183054</v>
+        <v>7183163</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,15 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515954</v>
+        <v>121515928</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594162</v>
+        <v>593793</v>
       </c>
       <c r="R16" t="n">
-        <v>7182918</v>
+        <v>7183160</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,15 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515933</v>
+        <v>121515929</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2326,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593834</v>
+        <v>593799</v>
       </c>
       <c r="R17" t="n">
-        <v>7183112</v>
+        <v>7183161</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,15 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515949</v>
+        <v>121515931</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594135</v>
+        <v>593808</v>
       </c>
       <c r="R18" t="n">
-        <v>7182928</v>
+        <v>7183154</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,15 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515940</v>
+        <v>121515933</v>
       </c>
       <c r="B19" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,34 +2530,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593895</v>
+        <v>593834</v>
       </c>
       <c r="R19" t="n">
-        <v>7183091</v>
+        <v>7183112</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,15 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515925</v>
+        <v>121515935</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,7 +2662,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2780,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593785</v>
+        <v>593842</v>
       </c>
       <c r="R20" t="n">
-        <v>7183163</v>
+        <v>7183114</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,7 +2706,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2716,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,15 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515935</v>
+        <v>121515938</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593842</v>
+        <v>593866</v>
       </c>
       <c r="R21" t="n">
-        <v>7183114</v>
+        <v>7183116</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2932,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,15 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121515942</v>
+        <v>121515939</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +2886,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3014,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593940</v>
+        <v>593874</v>
       </c>
       <c r="R22" t="n">
-        <v>7183055</v>
+        <v>7183112</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,15 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121515941</v>
+        <v>121515942</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,34 +2978,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593896</v>
+        <v>593940</v>
       </c>
       <c r="R23" t="n">
-        <v>7183092</v>
+        <v>7183055</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,15 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121515937</v>
+        <v>121515944</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593844</v>
+        <v>593959</v>
       </c>
       <c r="R24" t="n">
-        <v>7183109</v>
+        <v>7183054</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3149,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3159,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,15 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121515928</v>
+        <v>56145577</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,42 +3197,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593793</v>
+        <v>594109</v>
       </c>
       <c r="R25" t="n">
-        <v>7183160</v>
+        <v>7182941</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3385,22 +3251,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2015-07-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,35 +3267,44 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Niina Sallmén, Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121515924</v>
+        <v>121515951</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3467,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593759</v>
+        <v>594136</v>
       </c>
       <c r="R26" t="n">
-        <v>7183183</v>
+        <v>7182928</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3502,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,45 +3404,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121515953</v>
+        <v>121515954</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -3587,7 +3442,7 @@
         <v>594162</v>
       </c>
       <c r="R27" t="n">
-        <v>7182917</v>
+        <v>7182918</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3656,15 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121515947</v>
+        <v>121515953</v>
       </c>
       <c r="B28" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,34 +3522,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593958</v>
+        <v>594162</v>
       </c>
       <c r="R28" t="n">
-        <v>7183049</v>
+        <v>7182917</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3586,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3596,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,327 +3620,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>121515944</v>
-      </c>
-      <c r="B29" t="n">
-        <v>77553</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>593959</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7183054</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>121515951</v>
-      </c>
-      <c r="B30" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>594136</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7182928</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>130881603</v>
-      </c>
-      <c r="B31" t="n">
-        <v>91830</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Norrbotten, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>594019</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7183022</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Isabelle Holmström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Isabelle Holmström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
